--- a/data/all_datasets/REDD/REDD_House6_stats/2026-03-24.xlsx
+++ b/data/all_datasets/REDD/REDD_House6_stats/2026-03-24.xlsx
@@ -17927,7 +17927,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -18125,7 +18125,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>未知插座</t>
+          <t>未知设备</t>
         </is>
       </c>
       <c r="E14" t="n">
